--- a/output/yearly_total_coral_cover_iteration_87_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_87_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.270368212099411</v>
+        <v>1.298632728504677</v>
       </c>
       <c r="C3" t="n">
-        <v>4.619345696270269</v>
+        <v>4.58442493043021</v>
       </c>
       <c r="D3" t="n">
-        <v>6.083875890936561</v>
+        <v>6.10933260890768</v>
       </c>
       <c r="E3" t="n">
-        <v>11.97358979930624</v>
+        <v>11.99239026784257</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.425676592735379</v>
+        <v>1.492019875582472</v>
       </c>
       <c r="C4" t="n">
-        <v>5.099651518107014</v>
+        <v>4.981029683631919</v>
       </c>
       <c r="D4" t="n">
-        <v>6.374876182953188</v>
+        <v>6.372666870970879</v>
       </c>
       <c r="E4" t="n">
-        <v>12.90020429379558</v>
+        <v>12.84571643018527</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.633711483416974</v>
+        <v>1.75189112312498</v>
       </c>
       <c r="C5" t="n">
-        <v>5.709077042298584</v>
+        <v>5.462204698157808</v>
       </c>
       <c r="D5" t="n">
-        <v>6.642721437610891</v>
+        <v>6.70082267065302</v>
       </c>
       <c r="E5" t="n">
-        <v>13.98550996332645</v>
+        <v>13.91491849193581</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.868424317735521</v>
+        <v>2.057804931340825</v>
       </c>
       <c r="C6" t="n">
-        <v>6.426337308416377</v>
+        <v>6.052331885907056</v>
       </c>
       <c r="D6" t="n">
-        <v>6.957405858885954</v>
+        <v>7.161193564779516</v>
       </c>
       <c r="E6" t="n">
-        <v>15.25216748503785</v>
+        <v>15.2713303820274</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>2.125982852615498</v>
+        <v>2.396698905156917</v>
       </c>
       <c r="C7" t="n">
-        <v>7.249357077139411</v>
+        <v>6.727602006457517</v>
       </c>
       <c r="D7" t="n">
-        <v>7.3040587808955</v>
+        <v>7.630398863710738</v>
       </c>
       <c r="E7" t="n">
-        <v>16.67939871065041</v>
+        <v>16.75469977532517</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.320120311022038</v>
+        <v>1.578753528136787</v>
       </c>
       <c r="C8" t="n">
-        <v>4.829559713303299</v>
+        <v>4.366091640015592</v>
       </c>
       <c r="D8" t="n">
-        <v>5.567231195544917</v>
+        <v>5.928623544386188</v>
       </c>
       <c r="E8" t="n">
-        <v>11.71691121987025</v>
+        <v>11.87346871253857</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.649585809426672</v>
+        <v>2.023520716264462</v>
       </c>
       <c r="C9" t="n">
-        <v>5.810518195927418</v>
+        <v>5.193204329504016</v>
       </c>
       <c r="D9" t="n">
-        <v>6.03935723930955</v>
+        <v>6.525232618599289</v>
       </c>
       <c r="E9" t="n">
-        <v>13.49946124466364</v>
+        <v>13.74195766436777</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.99542435676034</v>
+        <v>2.495227205923154</v>
       </c>
       <c r="C10" t="n">
-        <v>6.912219959923562</v>
+        <v>6.117842805051001</v>
       </c>
       <c r="D10" t="n">
-        <v>6.47670992756533</v>
+        <v>7.098161134761367</v>
       </c>
       <c r="E10" t="n">
-        <v>15.38435424424923</v>
+        <v>15.71123114573552</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.348172425832589</v>
+        <v>2.992401548484889</v>
       </c>
       <c r="C11" t="n">
-        <v>8.111435206152985</v>
+        <v>7.109106143329481</v>
       </c>
       <c r="D11" t="n">
-        <v>6.938731276656763</v>
+        <v>7.683100677217561</v>
       </c>
       <c r="E11" t="n">
-        <v>17.39833890864234</v>
+        <v>17.78460836903193</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.718657779747797</v>
+        <v>3.512708774213005</v>
       </c>
       <c r="C12" t="n">
-        <v>9.411649533737243</v>
+        <v>8.163672292931047</v>
       </c>
       <c r="D12" t="n">
-        <v>7.507662860258791</v>
+        <v>8.227578085286137</v>
       </c>
       <c r="E12" t="n">
-        <v>19.63797017374383</v>
+        <v>19.90395915243019</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.112783106277235</v>
+        <v>4.035882584861134</v>
       </c>
       <c r="C13" t="n">
-        <v>10.77059473061898</v>
+        <v>9.241510586032435</v>
       </c>
       <c r="D13" t="n">
-        <v>8.003075141391516</v>
+        <v>8.854856076321203</v>
       </c>
       <c r="E13" t="n">
-        <v>21.88645297828774</v>
+        <v>22.13224924721477</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.824097051967616</v>
+        <v>2.332917252124653</v>
       </c>
       <c r="C14" t="n">
-        <v>7.68865532057932</v>
+        <v>6.574234231580596</v>
       </c>
       <c r="D14" t="n">
-        <v>6.096162369520568</v>
+        <v>6.715920060257496</v>
       </c>
       <c r="E14" t="n">
-        <v>15.6089147420675</v>
+        <v>15.62307154396274</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.897983384189231</v>
+        <v>2.458394426204438</v>
       </c>
       <c r="C15" t="n">
-        <v>8.202315536918293</v>
+        <v>6.887401931758286</v>
       </c>
       <c r="D15" t="n">
-        <v>6.132467399623616</v>
+        <v>6.813535234490756</v>
       </c>
       <c r="E15" t="n">
-        <v>16.23276632073114</v>
+        <v>16.15933159245348</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>2.239769029945716</v>
+        <v>2.927718916219626</v>
       </c>
       <c r="C16" t="n">
-        <v>9.634066936360716</v>
+        <v>8.009686819868026</v>
       </c>
       <c r="D16" t="n">
-        <v>6.579761471155505</v>
+        <v>7.49545718986059</v>
       </c>
       <c r="E16" t="n">
-        <v>18.45359743746194</v>
+        <v>18.43286292594824</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.820474402938945</v>
+        <v>2.394944072078967</v>
       </c>
       <c r="C17" t="n">
-        <v>8.849346178879198</v>
+        <v>7.336374791864436</v>
       </c>
       <c r="D17" t="n">
-        <v>6.116307832411714</v>
+        <v>7.069908829977768</v>
       </c>
       <c r="E17" t="n">
-        <v>16.78612841422986</v>
+        <v>16.80122769392117</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2.124452944604886</v>
+        <v>2.795222246054476</v>
       </c>
       <c r="C18" t="n">
-        <v>10.33032240821255</v>
+        <v>8.455753706769608</v>
       </c>
       <c r="D18" t="n">
-        <v>6.522564849906087</v>
+        <v>7.637643709866656</v>
       </c>
       <c r="E18" t="n">
-        <v>18.97734020272352</v>
+        <v>18.88861966269074</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2.175543095133889</v>
+        <v>2.866948733326748</v>
       </c>
       <c r="C19" t="n">
-        <v>11.06184225760093</v>
+        <v>8.948728498980103</v>
       </c>
       <c r="D19" t="n">
-        <v>6.614073553418932</v>
+        <v>7.845185174544432</v>
       </c>
       <c r="E19" t="n">
-        <v>19.85145890615376</v>
+        <v>19.66086240685128</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2.476723655842726</v>
+        <v>3.259814712135195</v>
       </c>
       <c r="C20" t="n">
-        <v>12.79025817831266</v>
+        <v>10.31460462746756</v>
       </c>
       <c r="D20" t="n">
-        <v>7.036293788584358</v>
+        <v>8.397536067907772</v>
       </c>
       <c r="E20" t="n">
-        <v>22.30327562273974</v>
+        <v>21.97195540751053</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.508779324317626</v>
+        <v>1.975178206174158</v>
       </c>
       <c r="C21" t="n">
-        <v>9.523659589541118</v>
+        <v>7.687545945673522</v>
       </c>
       <c r="D21" t="n">
-        <v>5.856468667528711</v>
+        <v>7.066129101316418</v>
       </c>
       <c r="E21" t="n">
-        <v>16.88890758138746</v>
+        <v>16.7288532531641</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_total_coral_cover_iteration_87_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_87_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.298632728504677</v>
+        <v>1.261620840054572</v>
       </c>
       <c r="C3" t="n">
-        <v>4.58442493043021</v>
+        <v>4.588990057254957</v>
       </c>
       <c r="D3" t="n">
-        <v>6.10933260890768</v>
+        <v>6.182109566223496</v>
       </c>
       <c r="E3" t="n">
-        <v>11.99239026784257</v>
+        <v>12.03272046353302</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.492019875582472</v>
+        <v>1.389606858837046</v>
       </c>
       <c r="C4" t="n">
-        <v>4.981029683631919</v>
+        <v>5.012183612862059</v>
       </c>
       <c r="D4" t="n">
-        <v>6.372666870970879</v>
+        <v>6.458794783686165</v>
       </c>
       <c r="E4" t="n">
-        <v>12.84571643018527</v>
+        <v>12.86058525538527</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.75189112312498</v>
+        <v>1.559713073287384</v>
       </c>
       <c r="C5" t="n">
-        <v>5.462204698157808</v>
+        <v>5.546810623009814</v>
       </c>
       <c r="D5" t="n">
-        <v>6.70082267065302</v>
+        <v>6.796805879653373</v>
       </c>
       <c r="E5" t="n">
-        <v>13.91491849193581</v>
+        <v>13.90332957595057</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>2.057804931340825</v>
+        <v>1.767443753217387</v>
       </c>
       <c r="C6" t="n">
-        <v>6.052331885907056</v>
+        <v>6.200460187372161</v>
       </c>
       <c r="D6" t="n">
-        <v>7.161193564779516</v>
+        <v>7.255409103578351</v>
       </c>
       <c r="E6" t="n">
-        <v>15.2713303820274</v>
+        <v>15.2233130441679</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>2.396698905156917</v>
+        <v>2.014239230622524</v>
       </c>
       <c r="C7" t="n">
-        <v>6.727602006457517</v>
+        <v>6.979507205577733</v>
       </c>
       <c r="D7" t="n">
-        <v>7.630398863710738</v>
+        <v>7.672073969416601</v>
       </c>
       <c r="E7" t="n">
-        <v>16.75469977532517</v>
+        <v>16.66582040561686</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.578753528136787</v>
+        <v>1.267516676377154</v>
       </c>
       <c r="C8" t="n">
-        <v>4.366091640015592</v>
+        <v>4.6670397662669</v>
       </c>
       <c r="D8" t="n">
-        <v>5.928623544386188</v>
+        <v>5.961723226684648</v>
       </c>
       <c r="E8" t="n">
-        <v>11.87346871253857</v>
+        <v>11.8962796693287</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.023520716264462</v>
+        <v>1.624926014669409</v>
       </c>
       <c r="C9" t="n">
-        <v>5.193204329504016</v>
+        <v>5.702868339790756</v>
       </c>
       <c r="D9" t="n">
-        <v>6.525232618599289</v>
+        <v>6.58052874763289</v>
       </c>
       <c r="E9" t="n">
-        <v>13.74195766436777</v>
+        <v>13.90832310209306</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.495227205923154</v>
+        <v>2.004785423533348</v>
       </c>
       <c r="C10" t="n">
-        <v>6.117842805051001</v>
+        <v>6.875710227227409</v>
       </c>
       <c r="D10" t="n">
-        <v>7.098161134761367</v>
+        <v>7.1525107884122</v>
       </c>
       <c r="E10" t="n">
-        <v>15.71123114573552</v>
+        <v>16.03300643917296</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.992401548484889</v>
+        <v>2.41377192199612</v>
       </c>
       <c r="C11" t="n">
-        <v>7.109106143329481</v>
+        <v>8.175512997918783</v>
       </c>
       <c r="D11" t="n">
-        <v>7.683100677217561</v>
+        <v>7.869414832322916</v>
       </c>
       <c r="E11" t="n">
-        <v>17.78460836903193</v>
+        <v>18.45869975223782</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.512708774213005</v>
+        <v>2.828801471253915</v>
       </c>
       <c r="C12" t="n">
-        <v>8.163672292931047</v>
+        <v>9.501006480903502</v>
       </c>
       <c r="D12" t="n">
-        <v>8.227578085286137</v>
+        <v>8.592753552932216</v>
       </c>
       <c r="E12" t="n">
-        <v>19.90395915243019</v>
+        <v>20.92256150508963</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.035882584861134</v>
+        <v>3.223179834554712</v>
       </c>
       <c r="C13" t="n">
-        <v>9.241510586032435</v>
+        <v>10.85140981751304</v>
       </c>
       <c r="D13" t="n">
-        <v>8.854856076321203</v>
+        <v>9.246321289861656</v>
       </c>
       <c r="E13" t="n">
-        <v>22.13224924721477</v>
+        <v>23.32091094192941</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.332917252124653</v>
+        <v>1.835740579739984</v>
       </c>
       <c r="C14" t="n">
-        <v>6.574234231580596</v>
+        <v>7.593720317578653</v>
       </c>
       <c r="D14" t="n">
-        <v>6.715920060257496</v>
+        <v>7.020566190362323</v>
       </c>
       <c r="E14" t="n">
-        <v>15.62307154396274</v>
+        <v>16.45002708768096</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>2.458394426204438</v>
+        <v>1.907889218525081</v>
       </c>
       <c r="C15" t="n">
-        <v>6.887401931758286</v>
+        <v>8.106928929973673</v>
       </c>
       <c r="D15" t="n">
-        <v>6.813535234490756</v>
+        <v>7.180826685603573</v>
       </c>
       <c r="E15" t="n">
-        <v>16.15933159245348</v>
+        <v>17.19564483410233</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>2.927718916219626</v>
+        <v>2.240790047558133</v>
       </c>
       <c r="C16" t="n">
-        <v>8.009686819868026</v>
+        <v>9.473443194468894</v>
       </c>
       <c r="D16" t="n">
-        <v>7.49545718986059</v>
+        <v>7.773890656262028</v>
       </c>
       <c r="E16" t="n">
-        <v>18.43286292594824</v>
+        <v>19.48812389828905</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2.394944072078967</v>
+        <v>1.818481455099325</v>
       </c>
       <c r="C17" t="n">
-        <v>7.336374791864436</v>
+        <v>8.697577801279682</v>
       </c>
       <c r="D17" t="n">
-        <v>7.069908829977768</v>
+        <v>7.308748411466932</v>
       </c>
       <c r="E17" t="n">
-        <v>16.80122769392117</v>
+        <v>17.82480766784594</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2.795222246054476</v>
+        <v>2.090337211882309</v>
       </c>
       <c r="C18" t="n">
-        <v>8.455753706769608</v>
+        <v>10.07857284441254</v>
       </c>
       <c r="D18" t="n">
-        <v>7.637643709866656</v>
+        <v>7.883119905836529</v>
       </c>
       <c r="E18" t="n">
-        <v>18.88861966269074</v>
+        <v>20.05202996213138</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2.866948733326748</v>
+        <v>2.11321193339126</v>
       </c>
       <c r="C19" t="n">
-        <v>8.948728498980103</v>
+        <v>10.73151360755301</v>
       </c>
       <c r="D19" t="n">
-        <v>7.845185174544432</v>
+        <v>8.091191514274596</v>
       </c>
       <c r="E19" t="n">
-        <v>19.66086240685128</v>
+        <v>20.93591705521887</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>3.259814712135195</v>
+        <v>2.366110142005238</v>
       </c>
       <c r="C20" t="n">
-        <v>10.31460462746756</v>
+        <v>12.35053338158051</v>
       </c>
       <c r="D20" t="n">
-        <v>8.397536067907772</v>
+        <v>8.647793375197327</v>
       </c>
       <c r="E20" t="n">
-        <v>21.97195540751053</v>
+        <v>23.36443689878308</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.975178206174158</v>
+        <v>1.409907513022929</v>
       </c>
       <c r="C21" t="n">
-        <v>7.687545945673522</v>
+        <v>9.124049004004497</v>
       </c>
       <c r="D21" t="n">
-        <v>7.066129101316418</v>
+        <v>7.283095343954963</v>
       </c>
       <c r="E21" t="n">
-        <v>16.7288532531641</v>
+        <v>17.81705186098239</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_total_coral_cover_iteration_87_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_87_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.261620840054572</v>
+        <v>2.610397945136501</v>
       </c>
       <c r="C3" t="n">
-        <v>4.588990057254957</v>
+        <v>7.689398618191053</v>
       </c>
       <c r="D3" t="n">
-        <v>6.182109566223496</v>
+        <v>8.214850260158947</v>
       </c>
       <c r="E3" t="n">
-        <v>12.03272046353302</v>
+        <v>18.5146468234865</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.389606858837046</v>
+        <v>1.128222769297518</v>
       </c>
       <c r="C4" t="n">
-        <v>5.012183612862059</v>
+        <v>4.423520665593178</v>
       </c>
       <c r="D4" t="n">
-        <v>6.458794783686165</v>
+        <v>5.736567707580853</v>
       </c>
       <c r="E4" t="n">
-        <v>12.86058525538527</v>
+        <v>11.28831114247155</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.559713073287384</v>
+        <v>1.274565788970949</v>
       </c>
       <c r="C5" t="n">
-        <v>5.546810623009814</v>
+        <v>4.944637499071216</v>
       </c>
       <c r="D5" t="n">
-        <v>6.796805879653373</v>
+        <v>6.056453799371797</v>
       </c>
       <c r="E5" t="n">
-        <v>13.90332957595057</v>
+        <v>12.27565708741396</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.767443753217387</v>
+        <v>1.433889698401489</v>
       </c>
       <c r="C6" t="n">
-        <v>6.200460187372161</v>
+        <v>5.592456729330701</v>
       </c>
       <c r="D6" t="n">
-        <v>7.255409103578351</v>
+        <v>6.405116417294835</v>
       </c>
       <c r="E6" t="n">
-        <v>15.2233130441679</v>
+        <v>13.43146284502703</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>2.014239230622524</v>
+        <v>1.599804714081241</v>
       </c>
       <c r="C7" t="n">
-        <v>6.979507205577733</v>
+        <v>6.354110072351298</v>
       </c>
       <c r="D7" t="n">
-        <v>7.672073969416601</v>
+        <v>6.752710838592141</v>
       </c>
       <c r="E7" t="n">
-        <v>16.66582040561686</v>
+        <v>14.70662562502468</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.267516676377154</v>
+        <v>1.778922483072495</v>
       </c>
       <c r="C8" t="n">
-        <v>4.6670397662669</v>
+        <v>7.230315102109251</v>
       </c>
       <c r="D8" t="n">
-        <v>5.961723226684648</v>
+        <v>7.107282875822762</v>
       </c>
       <c r="E8" t="n">
-        <v>11.8962796693287</v>
+        <v>16.11652046100451</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.624926014669409</v>
+        <v>1.960205917450196</v>
       </c>
       <c r="C9" t="n">
-        <v>5.702868339790756</v>
+        <v>8.215100043966624</v>
       </c>
       <c r="D9" t="n">
-        <v>6.58052874763289</v>
+        <v>7.567615464341531</v>
       </c>
       <c r="E9" t="n">
-        <v>13.90832310209306</v>
+        <v>17.74292142575835</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.004785423533348</v>
+        <v>1.20207152403388</v>
       </c>
       <c r="C10" t="n">
-        <v>6.875710227227409</v>
+        <v>6.185678125193793</v>
       </c>
       <c r="D10" t="n">
-        <v>7.1525107884122</v>
+        <v>5.968073746547487</v>
       </c>
       <c r="E10" t="n">
-        <v>16.03300643917296</v>
+        <v>13.35582339577516</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.41377192199612</v>
+        <v>1.159925095090564</v>
       </c>
       <c r="C11" t="n">
-        <v>8.175512997918783</v>
+        <v>6.391570253728435</v>
       </c>
       <c r="D11" t="n">
-        <v>7.869414832322916</v>
+        <v>5.83884629623748</v>
       </c>
       <c r="E11" t="n">
-        <v>18.45869975223782</v>
+        <v>13.39034164505648</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.828801471253915</v>
+        <v>1.279354703312189</v>
       </c>
       <c r="C12" t="n">
-        <v>9.501006480903502</v>
+        <v>7.420353490485709</v>
       </c>
       <c r="D12" t="n">
-        <v>8.592753552932216</v>
+        <v>6.263226376352248</v>
       </c>
       <c r="E12" t="n">
-        <v>20.92256150508963</v>
+        <v>14.96293457015015</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.223179834554712</v>
+        <v>1.020084952097648</v>
       </c>
       <c r="C13" t="n">
-        <v>10.85140981751304</v>
+        <v>6.949752728455001</v>
       </c>
       <c r="D13" t="n">
-        <v>9.246321289861656</v>
+        <v>5.736587455363131</v>
       </c>
       <c r="E13" t="n">
-        <v>23.32091094192941</v>
+        <v>13.70642513591578</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.835740579739984</v>
+        <v>1.126035164339964</v>
       </c>
       <c r="C14" t="n">
-        <v>7.593720317578653</v>
+        <v>8.01948466195641</v>
       </c>
       <c r="D14" t="n">
-        <v>7.020566190362323</v>
+        <v>6.114226527278711</v>
       </c>
       <c r="E14" t="n">
-        <v>16.45002708768096</v>
+        <v>15.25974635357509</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.907889218525081</v>
+        <v>1.111112599235413</v>
       </c>
       <c r="C15" t="n">
-        <v>8.106928929973673</v>
+        <v>8.550816336971828</v>
       </c>
       <c r="D15" t="n">
-        <v>7.180826685603573</v>
+        <v>6.206893693082567</v>
       </c>
       <c r="E15" t="n">
-        <v>17.19564483410233</v>
+        <v>15.86882262928981</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>2.240790047558133</v>
+        <v>1.236285431526881</v>
       </c>
       <c r="C16" t="n">
-        <v>9.473443194468894</v>
+        <v>9.957886599129484</v>
       </c>
       <c r="D16" t="n">
-        <v>7.773890656262028</v>
+        <v>6.651654855537499</v>
       </c>
       <c r="E16" t="n">
-        <v>19.48812389828905</v>
+        <v>17.84582688619387</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.818481455099325</v>
+        <v>0.7483862749473437</v>
       </c>
       <c r="C17" t="n">
-        <v>8.697577801279682</v>
+        <v>7.51872461045124</v>
       </c>
       <c r="D17" t="n">
-        <v>7.308748411466932</v>
+        <v>5.560609179376891</v>
       </c>
       <c r="E17" t="n">
-        <v>17.82480766784594</v>
+        <v>13.82772006477547</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2.090337211882309</v>
+        <v>0.5956459671206249</v>
       </c>
       <c r="C18" t="n">
-        <v>10.07857284441254</v>
+        <v>6.531125689887119</v>
       </c>
       <c r="D18" t="n">
-        <v>7.883119905836529</v>
+        <v>5.085237123503544</v>
       </c>
       <c r="E18" t="n">
-        <v>20.05202996213138</v>
+        <v>12.21200878051129</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2.11321193339126</v>
+        <v>0.7053660905472483</v>
       </c>
       <c r="C19" t="n">
-        <v>10.73151360755301</v>
+        <v>8.084054208464725</v>
       </c>
       <c r="D19" t="n">
-        <v>8.091191514274596</v>
+        <v>5.64063143475005</v>
       </c>
       <c r="E19" t="n">
-        <v>20.93591705521887</v>
+        <v>14.43005173376202</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2.366110142005238</v>
+        <v>0.8105210871491242</v>
       </c>
       <c r="C20" t="n">
-        <v>12.35053338158051</v>
+        <v>9.764501936346946</v>
       </c>
       <c r="D20" t="n">
-        <v>8.647793375197327</v>
+        <v>6.185452323221816</v>
       </c>
       <c r="E20" t="n">
-        <v>23.36443689878308</v>
+        <v>16.76047534671789</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.409907513022929</v>
+        <v>0.9142820020109695</v>
       </c>
       <c r="C21" t="n">
-        <v>9.124049004004497</v>
+        <v>11.4944984708625</v>
       </c>
       <c r="D21" t="n">
-        <v>7.283095343954963</v>
+        <v>6.708723849585367</v>
       </c>
       <c r="E21" t="n">
-        <v>17.81705186098239</v>
+        <v>19.11750432245884</v>
       </c>
     </row>
   </sheetData>
